--- a/data/carriers_data/electricity/import_limits.xlsx
+++ b/data/carriers_data/electricity/import_limits.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9256858D-9C68-4626-B44C-34678D0EE5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1176" yWindow="13908" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="power_limits" sheetId="1" r:id="rId1"/>
@@ -349,9 +349,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -359,7 +359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -370,7 +370,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2030</v>
       </c>
@@ -381,7 +381,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2040</v>
       </c>
@@ -392,7 +392,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2050</v>
       </c>
